--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 24.11.2025 a 30.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 24.11.2025 a 30.11.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29523"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE6721C8-CC8C-48AC-91CB-50BD7E1810F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{299FD3B5-2B57-45F3-9E43-9A0C988DE999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="24.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="132">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -299,6 +299,187 @@
   </si>
   <si>
     <t xml:space="preserve">SUPERMERCADO E PADAR                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE APARECIDA GONCALVES RODRIGUES      </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa d
+a apólice anterior 2024/2025 ou CI atual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELINEIDE DIAS CAMPOS                         </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARYNAIRY RAYNA CARRARA NERO                  </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNA DA LOMBA STREFEZZA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDWIL APARECIDA DE LUCCA GATTAS              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANADIR TEIXEIRA DA SILVA LIMA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILMAR SIQUEIRA LEITE                        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 24.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMERIO DE LIMA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA JOUGLARD SCHEIN                      </t>
+  </si>
+  <si>
+    <t>Por gentileza providenciar o cancelamento da apólice com término d
+e vigência em 2026,e nos enviar uma cópia deste endosso já emitido
+, para que possamos prosseguir com a emissão desta proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOUISNORD FLEGOR                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATIA CRISTINA SOUZA SANTOS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRO MEDEIROS GOUVEIA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADJANE BARBOSA DE ARAUJO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULINA ROSA MARQUES DO PRADO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA DE ANDRADE                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSELIA MOUSINHO TAVARES DA SILVA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCADO AVENIDA LTDA ME                      </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não h
+á possibilidade efetuar a transferência de bônus para a empresa ME
+RCADOAVENIDA LTDA ME, pois o(a) senhor(a) MARIA PAULA DE OLIVEIRA
+DIANA, não consta no quadro de sócios da empresa. &lt;br&gt;Neste caso
+estamos nesta data efetuando a recusa desta proposta. Orientamos t
+ransmitirum novo processo como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACEA MILA MAGALHAES MARTINS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAROLYN AQUINO LOURENCO                      </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo em duplicidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C CAETANO DA SILVA RESTAURANTE ME            </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO, FOTO DO CHASSI, FOTO DE FOTO Justificativa de Dados Divergentes: PRAZO EXPIRADO, FOTO DO CHASSI, FOTO DE FOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO DE SANTANA ALMEIDA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO LEANDRO GOMES AGUIAR                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL PHILIPI FERNANDES DE SOUZA           </t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+"PENDÊNCIA 812 - Veículo informado é diferente do calculado&lt;br&gt;&lt;b
+r&gt;Constatamos que o modelo do veículo informado na cotação difere
+do constado, segue abaixo informação retornada pelo sistema atravé
+s do chassi do veículo: &lt;br&gt;&lt;br&gt;Modelo constatado: YAMAHA XTZ 150
+CROSSER &lt;br&gt;&lt;br&gt;FIPE: 827108-9 R$ 21.321,00&lt;br&gt;&lt;br&gt;Valor do prêmi
+o: 10x R$ 61,87&lt;br&gt;&lt;br&gt;Franquia: R$ 3.314,69 &lt;br&gt;&lt;br&gt;Podemos emiti
+r desse forma?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE WENDELL WILLAMS BARROS                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARINA APARECIDA ROMANI                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGICELIA ESPIRITO SANTO DA SILVA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAN RODRIGUES                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANETA PE BOUTIQUE E ACESSORIOS LTDA EPP    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALQUIRIA DE SOUZA CARDINOT                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO LUIZ DIAS MAGALHAES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LUCIRENE DE SENA                       </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: </t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>EDINALVA BATISTA DE ALBUQUERQUE OLIMPIO CPF 4311938438</t>
+  </si>
+  <si>
+    <t>Sem retorno</t>
+  </si>
+  <si>
+    <t>SAULO BATISTA NASCIMENTO CPF 22291284851</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
   </si>
 </sst>
 </file>
@@ -537,7 +718,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -586,7 +767,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -610,10 +790,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -647,11 +823,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -659,21 +834,73 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1052,25 +1279,25 @@
       <c r="B2" s="7">
         <v>45975</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="25">
         <v>45985</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="43">
         <v>135401772</v>
       </c>
       <c r="E2" s="17">
         <v>3450147096</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1081,25 +1308,25 @@
       <c r="B3" s="7">
         <v>45977</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>45985</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="43">
         <v>135416176</v>
       </c>
       <c r="E3" s="17">
         <v>3450148350</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="48">
+      <c r="I3" s="44">
         <v>45977</v>
       </c>
     </row>
@@ -1110,25 +1337,25 @@
       <c r="B4" s="7">
         <v>45975</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>45985</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="43">
         <v>135424757</v>
       </c>
       <c r="E4" s="17">
         <v>3450148251</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1139,25 +1366,25 @@
       <c r="B5" s="7">
         <v>45979</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>45985</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="43">
         <v>135436845</v>
       </c>
       <c r="E5" s="17">
         <v>3450150033</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1168,25 +1395,25 @@
       <c r="B6" s="7">
         <v>45979</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>45985</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="43">
         <v>135455689</v>
       </c>
       <c r="E6" s="17">
         <v>3450151860</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1197,25 +1424,25 @@
       <c r="B7" s="7">
         <v>45982</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>45985</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="43">
         <v>135447706</v>
       </c>
       <c r="E7" s="17">
         <v>3450150979</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="G7" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="48">
+      <c r="I7" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1226,25 +1453,25 @@
       <c r="B8" s="7">
         <v>45979</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>45985</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="43">
         <v>135447865</v>
       </c>
       <c r="E8" s="17">
         <v>3450151023</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="46" t="s">
+      <c r="G8" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1255,25 +1482,25 @@
       <c r="B9" s="7">
         <v>45980</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>45985</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="43">
         <v>135460163</v>
       </c>
       <c r="E9" s="17">
         <v>3450152024</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="49" t="s">
+      <c r="H9" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9" s="44">
         <v>45980</v>
       </c>
     </row>
@@ -1284,25 +1511,25 @@
       <c r="B10" s="7">
         <v>45978</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>45985</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="43">
         <v>135430722</v>
       </c>
       <c r="E10" s="17">
         <v>3450149615</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1313,25 +1540,25 @@
       <c r="B11" s="7">
         <v>45979</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>45985</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="43">
         <v>135465542</v>
       </c>
       <c r="E11" s="17">
         <v>3450150847</v>
       </c>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="46" t="s">
+      <c r="G11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="48">
+      <c r="I11" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1342,25 +1569,25 @@
       <c r="B12" s="7">
         <v>45975</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>45985</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="43">
         <v>135411669</v>
       </c>
       <c r="E12" s="17">
         <v>3450148108</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="46" t="s">
+      <c r="G12" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1371,25 +1598,25 @@
       <c r="B13" s="7">
         <v>45979</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>45985</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="43">
         <v>135453300</v>
       </c>
       <c r="E13" s="17">
         <v>3450151551</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="49" t="s">
+      <c r="H13" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1400,25 +1627,25 @@
       <c r="B14" s="7">
         <v>45978</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>45985</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="43">
         <v>135429256</v>
       </c>
       <c r="E14" s="17">
         <v>3450149439</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1429,25 +1656,25 @@
       <c r="B15" s="7">
         <v>45978</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>45985</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="43">
         <v>135426886</v>
       </c>
       <c r="E15" s="17">
         <v>3450149153</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="46" t="s">
+      <c r="G15" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1458,25 +1685,25 @@
       <c r="B16" s="7">
         <v>45973</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>45985</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="43">
         <v>135369003</v>
       </c>
       <c r="E16" s="17">
         <v>3450144599</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1487,25 +1714,25 @@
       <c r="B17" s="7">
         <v>45979</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>45985</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="43">
         <v>135349448</v>
       </c>
       <c r="E17" s="17">
         <v>3450143136</v>
       </c>
-      <c r="F17" s="45" t="s">
+      <c r="F17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1516,25 +1743,25 @@
       <c r="B18" s="7">
         <v>45989</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>45985</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="43">
         <v>135341393</v>
       </c>
       <c r="E18" s="17">
         <v>3450142234</v>
       </c>
-      <c r="F18" s="45" t="s">
+      <c r="F18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1545,25 +1772,25 @@
       <c r="B19" s="7">
         <v>45979</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <v>45985</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="43">
         <v>135453744</v>
       </c>
       <c r="E19" s="17">
         <v>3450151640</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1574,25 +1801,25 @@
       <c r="B20" s="7">
         <v>45979</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>45985</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="43">
         <v>135441593</v>
       </c>
       <c r="E20" s="17">
         <v>3450150275</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1603,25 +1830,25 @@
       <c r="B21" s="7">
         <v>45978</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>45985</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="43">
         <v>135421095</v>
       </c>
       <c r="E21" s="17">
         <v>3450148670</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H21" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1632,25 +1859,25 @@
       <c r="B22" s="7">
         <v>45964</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>45985</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="43">
         <v>135209200</v>
       </c>
       <c r="E22" s="17">
         <v>3450131047</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="51" t="s">
+      <c r="H22" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="44">
         <v>45973</v>
       </c>
     </row>
@@ -1661,25 +1888,25 @@
       <c r="B23" s="7">
         <v>45980</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <v>45985</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="43">
         <v>135465046</v>
       </c>
       <c r="E23" s="17">
         <v>3450152541</v>
       </c>
-      <c r="F23" s="45" t="s">
+      <c r="F23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="46" t="s">
+      <c r="G23" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="44">
         <v>45980</v>
       </c>
     </row>
@@ -1690,25 +1917,25 @@
       <c r="B24" s="7">
         <v>45979</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>45985</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="43">
         <v>135443260</v>
       </c>
       <c r="E24" s="17">
         <v>3450150528</v>
       </c>
-      <c r="F24" s="45" t="s">
+      <c r="F24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="46" t="s">
+      <c r="G24" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1719,25 +1946,25 @@
       <c r="B25" s="7">
         <v>45980</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="25">
         <v>45985</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="43">
         <v>135466041</v>
       </c>
       <c r="E25" s="17">
         <v>3450152761</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="46" t="s">
+      <c r="G25" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="H25" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="48">
+      <c r="I25" s="44">
         <v>45982</v>
       </c>
     </row>
@@ -1748,25 +1975,25 @@
       <c r="B26" s="7">
         <v>45978</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="25">
         <v>45985</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="43">
         <v>135430362</v>
       </c>
       <c r="E26" s="17">
         <v>3450149593</v>
       </c>
-      <c r="F26" s="45" t="s">
+      <c r="F26" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="46" t="s">
+      <c r="G26" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1777,25 +2004,25 @@
       <c r="B27" s="7">
         <v>45979</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="25">
         <v>45985</v>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="43">
         <v>135451102</v>
       </c>
       <c r="E27" s="17">
         <v>3450151386</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="49" t="s">
+      <c r="H27" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="44">
         <v>45979</v>
       </c>
     </row>
@@ -1806,25 +2033,25 @@
       <c r="B28" s="7">
         <v>45978</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="25">
         <v>45985</v>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="43">
         <v>135466627</v>
       </c>
       <c r="E28" s="17">
         <v>3450148526</v>
       </c>
-      <c r="F28" s="45" t="s">
+      <c r="F28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="46" t="s">
+      <c r="G28" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="48">
+      <c r="I28" s="44">
         <v>45978</v>
       </c>
     </row>
@@ -1832,28 +2059,28 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="52">
+      <c r="B29" s="47">
         <v>45975</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="25">
         <v>45985</v>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="43">
         <v>135397039</v>
       </c>
       <c r="E29" s="17">
         <v>3450146678</v>
       </c>
-      <c r="F29" s="45" t="s">
+      <c r="F29" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G29" s="46" t="s">
+      <c r="G29" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="49" t="s">
+      <c r="H29" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="48">
+      <c r="I29" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1864,25 +2091,25 @@
       <c r="B30" s="7">
         <v>45975</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="25">
         <v>45985</v>
       </c>
-      <c r="D30" s="47">
+      <c r="D30" s="43">
         <v>135398313</v>
       </c>
       <c r="E30" s="17">
         <v>3450146788</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="48">
+      <c r="I30" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1893,25 +2120,25 @@
       <c r="B31" s="7">
         <v>45974</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="25">
         <v>45985</v>
       </c>
-      <c r="D31" s="47">
+      <c r="D31" s="43">
         <v>135399941</v>
       </c>
       <c r="E31" s="17">
         <v>3450146425</v>
       </c>
-      <c r="F31" s="45" t="s">
+      <c r="F31" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G31" s="46" t="s">
+      <c r="G31" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="48">
+      <c r="I31" s="44">
         <v>45974</v>
       </c>
     </row>
@@ -1922,25 +2149,25 @@
       <c r="B32" s="7">
         <v>45975</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="25">
         <v>45985</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D32" s="43">
         <v>135400989</v>
       </c>
       <c r="E32" s="17">
         <v>3450147020</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="46" t="s">
+      <c r="G32" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="48">
+      <c r="I32" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1951,25 +2178,25 @@
       <c r="B33" s="7">
         <v>45975</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="25">
         <v>45985</v>
       </c>
-      <c r="D33" s="47">
+      <c r="D33" s="43">
         <v>135407001</v>
       </c>
       <c r="E33" s="17">
         <v>3450147624</v>
       </c>
-      <c r="F33" s="45" t="s">
+      <c r="F33" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="46" t="s">
+      <c r="G33" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -1980,25 +2207,25 @@
       <c r="B34" s="7">
         <v>45975</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="25">
         <v>45985</v>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="43">
         <v>135407729</v>
       </c>
       <c r="E34" s="17">
         <v>3450147657</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G34" s="46" t="s">
+      <c r="G34" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="48">
+      <c r="I34" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2009,25 +2236,25 @@
       <c r="B35" s="7">
         <v>45975</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="25">
         <v>45985</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="43">
         <v>135408921</v>
       </c>
       <c r="E35" s="17">
         <v>3450147778</v>
       </c>
-      <c r="F35" s="45" t="s">
+      <c r="F35" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="46" t="s">
+      <c r="G35" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I35" s="48">
+      <c r="I35" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2038,25 +2265,25 @@
       <c r="B36" s="7">
         <v>45986</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="25">
         <v>45985</v>
       </c>
-      <c r="D36" s="47">
+      <c r="D36" s="43">
         <v>135441855</v>
       </c>
       <c r="E36" s="17">
         <v>3450147866</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="46" t="s">
+      <c r="G36" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H36" s="53" t="s">
+      <c r="H36" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I36" s="48">
+      <c r="I36" s="44">
         <v>45985</v>
       </c>
     </row>
@@ -2067,25 +2294,25 @@
       <c r="B37" s="7">
         <v>45975</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="25">
         <v>45985</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="43">
         <v>135410250</v>
       </c>
       <c r="E37" s="17">
         <v>3450147899</v>
       </c>
-      <c r="F37" s="45" t="s">
+      <c r="F37" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="46" t="s">
+      <c r="G37" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I37" s="48">
+      <c r="I37" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2096,25 +2323,25 @@
       <c r="B38" s="7">
         <v>45975</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="25">
         <v>45985</v>
       </c>
-      <c r="D38" s="47">
+      <c r="D38" s="43">
         <v>135410697</v>
       </c>
       <c r="E38" s="17">
         <v>3450147943</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I38" s="48">
+      <c r="I38" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2125,25 +2352,25 @@
       <c r="B39" s="7">
         <v>45975</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="25">
         <v>45985</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="43">
         <v>135412025</v>
       </c>
       <c r="E39" s="17">
         <v>3450148163</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G39" s="46" t="s">
+      <c r="G39" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H39" s="53" t="s">
+      <c r="H39" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I39" s="48">
+      <c r="I39" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2154,25 +2381,25 @@
       <c r="B40" s="7">
         <v>45975</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="25">
         <v>45985</v>
       </c>
-      <c r="D40" s="47">
+      <c r="D40" s="43">
         <v>135412039</v>
       </c>
       <c r="E40" s="17">
         <v>3450148185</v>
       </c>
-      <c r="F40" s="45" t="s">
+      <c r="F40" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G40" s="46" t="s">
+      <c r="G40" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I40" s="48">
+      <c r="I40" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2183,25 +2410,25 @@
       <c r="B41" s="7">
         <v>45975</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="25">
         <v>45985</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D41" s="43">
         <v>135412102</v>
       </c>
       <c r="E41" s="17">
         <v>3450148196</v>
       </c>
-      <c r="F41" s="45" t="s">
+      <c r="F41" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="46" t="s">
+      <c r="G41" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I41" s="48">
+      <c r="I41" s="44">
         <v>45975</v>
       </c>
     </row>
@@ -2212,25 +2439,25 @@
       <c r="B42" s="7">
         <v>45975</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="25">
         <v>45985</v>
       </c>
-      <c r="D42" s="47">
+      <c r="D42" s="43">
         <v>135413036</v>
       </c>
       <c r="E42" s="17">
         <v>3450148273</v>
       </c>
-      <c r="F42" s="45" t="s">
+      <c r="F42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G42" s="46" t="s">
+      <c r="G42" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I42" s="55">
+      <c r="I42" s="49">
         <v>45975</v>
       </c>
     </row>
@@ -2242,7 +2469,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
       <c r="G43" s="6"/>
-      <c r="H43" s="54"/>
+      <c r="H43" s="48"/>
       <c r="I43" s="12"/>
     </row>
   </sheetData>
@@ -2265,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2280,671 +2507,958 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="25"/>
+      <c r="A2" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="56">
+        <v>45977</v>
+      </c>
+      <c r="C2" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D2" s="62">
+        <v>135367670</v>
+      </c>
+      <c r="E2" s="59">
+        <v>3450144500</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="61">
+        <v>45985</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C3" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D3" s="63">
+        <v>135362829</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450143884</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="44">
+        <v>45982</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C4" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D4" s="63">
+        <v>135370895</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450144797</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="44">
+        <v>45980</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C5" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D5" s="63">
+        <v>135418067</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450148405</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="44">
+        <v>45978</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C6" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D6" s="63">
+        <v>135431815</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450149747</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="44">
+        <v>45978</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C7" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D7" s="63">
+        <v>135475935</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450153839</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" s="44">
+        <v>45980</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C8" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D8" s="63">
+        <v>135469811</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450153201</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="7">
+        <v>46004</v>
+      </c>
+      <c r="C9" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D9" s="63">
+        <v>135475033</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450153740</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="44">
+        <v>45974</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="7">
+        <v>45987</v>
+      </c>
+      <c r="C10" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D10" s="63">
+        <v>135365526</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450144247</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="44">
+        <v>45982</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C11" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D11" s="63">
+        <v>135466743</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450152849</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="44">
+        <v>45980</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C12" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D12" s="63">
+        <v>135487600</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450154367</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="7">
+        <v>45995</v>
+      </c>
+      <c r="C13" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D13" s="63">
+        <v>135470636</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450153245</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C14" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D14" s="63">
+        <v>135491304</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450154697</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="44">
+        <v>45982</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C15" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D15" s="63">
+        <v>135493505</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450154994</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="25"/>
+      <c r="B16" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C16" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D16" s="63">
+        <v>135464753</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450152497</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="25"/>
+      <c r="B17" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C17" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D17" s="63">
+        <v>135490210</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450154610</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="44">
+        <v>45982</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45974</v>
+      </c>
+      <c r="C18" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D18" s="63">
+        <v>135423401</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450145600</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C19" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D19" s="63">
+        <v>135513778</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450156810</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C20" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D20" s="63">
+        <v>135371138</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450144808</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C21" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D21" s="63">
+        <v>135422961</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450148780</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="44">
+        <v>45978</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="25"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C22" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D22" s="63">
+        <v>135465259</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450150825</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="44">
+        <v>45979</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="25"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45974</v>
+      </c>
+      <c r="C23" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D23" s="63">
+        <v>135384088</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450145776</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="25"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45974</v>
+      </c>
+      <c r="C24" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D24" s="63">
+        <v>135380282</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450145380</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="44">
+        <v>45979</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="25"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C25" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D25" s="63">
+        <v>135424489</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450148933</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="44">
+        <v>45978</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C26" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D26" s="63">
+        <v>135421815</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450148724</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="I26" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="25"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C27" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D27" s="63">
+        <v>135427573</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450149230</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="44">
+        <v>45978</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="25"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45975</v>
+      </c>
+      <c r="C28" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D28" s="63">
+        <v>135443033</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450147481</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="44">
+        <v>45975</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="25"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45982</v>
+      </c>
+      <c r="C29" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D29" s="63">
+        <v>135497978</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450155478</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="44">
+        <v>45982</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="25"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C30" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D30" s="63">
+        <v>135440916</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450150210</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="44">
+        <v>45979</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="25"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C31" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D31" s="63">
+        <v>135442838</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450150484</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="44">
+        <v>45979</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="25"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C32" s="57">
+        <v>45986</v>
+      </c>
+      <c r="D32" s="63">
+        <v>135460460</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450152080</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" s="44">
+        <v>45980</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="25"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="25"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="25"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:F32">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2964,7 +3478,7 @@
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="25" customWidth="1"/>
+    <col min="9" max="9" width="21" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2992,7 +3506,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3000,36 +3514,64 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="64">
+        <v>45991</v>
+      </c>
+      <c r="C2" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450150880</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="11"/>
+      <c r="B3" s="64">
+        <v>45991</v>
+      </c>
+      <c r="C3" s="25">
+        <v>45982</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450155071</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="24"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:9">
@@ -3037,8 +3579,8 @@
         <v>9</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
@@ -3049,8 +3591,8 @@
         <v>9</v>
       </c>
       <c r="B6" s="6"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
       <c r="G6" s="19"/>
@@ -3061,8 +3603,8 @@
         <v>9</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="27"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
       <c r="G7" s="19"/>
@@ -3073,8 +3615,8 @@
         <v>9</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
       <c r="G8" s="19"/>
@@ -3085,23 +3627,23 @@
         <v>9</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="9"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="23"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="22"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:9">
@@ -3109,8 +3651,8 @@
         <v>9</v>
       </c>
       <c r="B11" s="6"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="26"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
       <c r="G11" s="19"/>
@@ -3121,11 +3663,11 @@
         <v>9</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="23"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="21"/>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:9">
@@ -3133,8 +3675,8 @@
         <v>9</v>
       </c>
       <c r="B13" s="6"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="26"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
       <c r="G13" s="19"/>
@@ -3145,8 +3687,8 @@
         <v>9</v>
       </c>
       <c r="B14" s="6"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="26"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
       <c r="G14" s="19"/>
@@ -3157,8 +3699,8 @@
         <v>9</v>
       </c>
       <c r="B15" s="6"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
       <c r="G15" s="19"/>
@@ -3169,18 +3711,18 @@
         <v>9</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
       <c r="G16" s="19"/>
-      <c r="H16" s="9"/>
+      <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="26"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
       <c r="G17" s="19"/>
@@ -3189,18 +3731,18 @@
     <row r="18" spans="1:8">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="23"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="22"/>
+      <c r="G18" s="21"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="26"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
       <c r="G19" s="19"/>
@@ -3209,8 +3751,8 @@
     <row r="20" spans="1:8">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
       <c r="G20" s="19"/>
@@ -3219,8 +3761,8 @@
     <row r="21" spans="1:8">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
       <c r="G21" s="19"/>
@@ -3229,8 +3771,8 @@
     <row r="22" spans="1:8">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="27"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
       <c r="G22" s="19"/>
@@ -3239,8 +3781,8 @@
     <row r="23" spans="1:8">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
       <c r="G23" s="19"/>
@@ -3249,18 +3791,18 @@
     <row r="24" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="23"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="22"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="22"/>
+      <c r="G24" s="21"/>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
       <c r="G25" s="19"/>
@@ -3269,8 +3811,8 @@
     <row r="26" spans="1:8">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
       <c r="G26" s="19"/>
@@ -3279,8 +3821,8 @@
     <row r="27" spans="1:8">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
       <c r="G27" s="19"/>
@@ -3289,8 +3831,8 @@
     <row r="28" spans="1:8">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="27"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="26"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
       <c r="G28" s="19"/>
@@ -3299,89 +3841,89 @@
     <row r="29" spans="1:8">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="23"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="22"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="22"/>
+      <c r="G29" s="21"/>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="23"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="22"/>
+      <c r="G30" s="21"/>
       <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="22"/>
+      <c r="G31" s="21"/>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="23"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="22"/>
+      <c r="G32" s="21"/>
       <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="23"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="22"/>
+      <c r="G33" s="21"/>
       <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="23"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="22"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="22"/>
+      <c r="G34" s="21"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="23"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="22"/>
+      <c r="G35" s="21"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="23"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="22"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="22"/>
+      <c r="G36" s="21"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="14"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
@@ -3519,12 +4061,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="27"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="28"/>
+      <c r="G2" s="27"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -3532,12 +4074,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="27"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="28"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="25"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3545,12 +4087,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="27"/>
+      <c r="D4" s="26"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="28"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3558,12 +4100,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3571,12 +4113,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="27"/>
+      <c r="D6" s="26"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="28"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3584,12 +4126,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="27"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="25"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -3597,12 +4139,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="28"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="25"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -3610,12 +4152,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="26"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="25"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -3623,12 +4165,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="26"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="28"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="25"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -3636,12 +4178,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="26"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="25"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -3649,12 +4191,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="26"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="28"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="25"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -3662,12 +4204,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="26"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="28"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -3675,12 +4217,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="26"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="28"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="25"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -3688,23 +4230,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="26"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="28"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="25"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="26"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="28"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="25"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -3715,7 +4257,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="25"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -3726,7 +4268,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="25"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -3737,7 +4279,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -3748,7 +4290,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4167,63 +4709,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="36"/>
+      <c r="I3" s="33"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -4750,7 +5292,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4762,232 +5304,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="25"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="25"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="25"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="23"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="25"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="23"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="25"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="25"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="23"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="25"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="23"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="25"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="23"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="25"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="23"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="25"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="25"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="25"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="25"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="23"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="25"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="23"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="25"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="23"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="25"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="32"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="29"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4996,9 +5538,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="32"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5007,9 +5549,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="32"/>
+      <c r="G21" s="29"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -5018,9 +5560,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="32"/>
+      <c r="G22" s="29"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="25"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5029,9 +5571,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="32"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="25"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5040,9 +5582,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="29"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="25"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5053,7 +5595,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="25"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5064,7 +5606,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="25"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5075,7 +5617,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="25"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -5086,7 +5628,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="25"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -5097,7 +5639,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="25"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -5108,7 +5650,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="25"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -5119,7 +5661,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="25"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -5130,7 +5672,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="25"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -5141,7 +5683,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="25"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -5152,7 +5694,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="25"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -5163,7 +5705,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="25"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -5451,462 +5993,462 @@
     <row r="2" spans="1:9">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="43"/>
       <c r="E2" s="17"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="48"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="43"/>
       <c r="E3" s="17"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="48"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="47"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="17"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="48"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="47"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="43"/>
       <c r="E5" s="17"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="48"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="47"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="43"/>
       <c r="E6" s="17"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="48"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="44"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="48"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="44"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="47"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="17"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="48"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="44"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="47"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="43"/>
       <c r="E9" s="17"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="48"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="44"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="47"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="17"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="48"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="44"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="47"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="43"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="48"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="44"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="47"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="43"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="48"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="47"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="43"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="48"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="44"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="47"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="43"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="48"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="44"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="47"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="48"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="44"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="47"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="43"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="48"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="44"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="47"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="43"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="48"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="44"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="47"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="43"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="48"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="47"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="48"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="47"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="43"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="48"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="47"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="48"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="47"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="43"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="48"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="47"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="43"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="48"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="47"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="43"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="48"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="47"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="43"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="48"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="47"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="43"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="48"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="47"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="43"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="48"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="47"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="43"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="48"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="43"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="48"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="47"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="43"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="48"/>
+      <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="47"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="43"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="48"/>
+      <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="47"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="43"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="46"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="48"/>
+      <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="47"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="43"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="48"/>
+      <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="47"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="43"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="46"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="42"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="48"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="47"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="43"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="46"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="42"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="48"/>
+      <c r="I35" s="44"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="47"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="43"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="48"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="44"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="47"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="43"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="46"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="48"/>
+      <c r="I37" s="44"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="47"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="46"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="48"/>
+      <c r="I38" s="44"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="47"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="43"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="48"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="44"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="47"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="43"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="46"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="42"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="48"/>
+      <c r="I40" s="44"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="47"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="43"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="46"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="42"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="48"/>
+      <c r="I41" s="44"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="47"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="43"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="46"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="42"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="48"/>
+      <c r="I42" s="44"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="46"/>
+      <c r="G43" s="42"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -5929,8 +6471,67 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="cda820598d61c00a5299587a11c0dc14">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0803c1971eb453546b9f8a0aa56ab91b" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -5979,12 +6580,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -5993,12 +6594,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6081,7 +6682,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6100,7 +6701,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6133,7 +6734,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6216,8 +6817,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6306,7 +6907,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517949</_dlc_DocId>
@@ -6349,77 +6950,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A83BFBCA-B134-4A28-B007-EA254E13EDD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2EF5E87-F613-441E-A63A-5260576F6967}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 24.11.2025 a 30.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 24.11.2025 a 30.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{299FD3B5-2B57-45F3-9E43-9A0C988DE999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA05203-6854-4531-BE33-717AD6415AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="24.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="161">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -480,6 +480,101 @@
   </si>
   <si>
     <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>RS TELECOMUNICACOES LTDA ME CNPJ 30995261000150</t>
+  </si>
+  <si>
+    <t>R N DE SOUSA ADEGA ME CNPJ 41928423000153</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENIS DI LALLO                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIOGENES DE OLIVEIRA E SOUZA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA MACHADO DE AGUIAR SANTOS              </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 25.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INNOVARE CONSTRUCAO E INCORPORACAO LTDA ME   </t>
+  </si>
+  <si>
+    <t>KM INDISPONIVEL ## FRUSTRADO ## FOTO ESCURA PRAZO EXPIRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO DE SOUZA DIAS JUNIOR                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ROSANGELA POLICARPO                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: PAINEL DO VEICULO LIGADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE EDUARDO YOSHIDA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVIA MOUTINHO PEREIRA                       </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade&lt;br&gt;&lt;br&gt;Informamos que a pr
+oposta em questão se encontra em duplicidade com a proposta 133025
+681 a qual já se encontra emitida pela apl 5177202551311225808, pa
+ra prosseguirmos com a emissão se faz necessário realizar o cancel
+amento da mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE GILBERTO AGUIAR DE ARRUDA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO AQUINO DA SILVA                       </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade&lt;br&gt;&lt;br&gt;Informamos que a pr
+oposta em questão se encontra em duplicidade com a proposta 132278
+180 a qual já se encontra emitida pela apl 5177202551310821926, pa
+ra prosseguir com a emissão, necessitamos do cancelamento daa mesm
+a. Por gentileza providenciar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE BARBOSA DE MELO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO CESAR DE GRANDE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOANA D ARC CAVALCANTE DE BRITO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO RODRIGUES DOS SANTOS                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO Fotos que tiveram repique: Número do Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFIGENIA MARIA FERRAZ DE ARAUJO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANE DE LIMA POPUASKI                     </t>
   </si>
 </sst>
 </file>
@@ -538,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -713,12 +808,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -841,7 +969,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -863,7 +990,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -873,16 +999,37 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2507,60 +2654,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="56">
+      <c r="A2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="55">
         <v>45977</v>
       </c>
-      <c r="C2" s="57">
+      <c r="C2" s="56">
         <v>45986</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="60">
         <v>135367670</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="57">
         <v>3450144500</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="61">
+      <c r="I2" s="59">
         <v>45985</v>
       </c>
     </row>
@@ -2571,22 +2718,22 @@
       <c r="B3" s="7">
         <v>45973</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="56">
         <v>45986</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="22">
         <v>135362829</v>
       </c>
       <c r="E3" s="17">
         <v>3450143884</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G3" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="H3" s="12" t="s">
         <v>81</v>
       </c>
       <c r="I3" s="44">
@@ -2600,22 +2747,22 @@
       <c r="B4" s="7">
         <v>45978</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="56">
         <v>45986</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="22">
         <v>135370895</v>
       </c>
       <c r="E4" s="17">
         <v>3450144797</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="12" t="s">
         <v>83</v>
       </c>
       <c r="I4" s="44">
@@ -2629,16 +2776,16 @@
       <c r="B5" s="7">
         <v>45978</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="56">
         <v>45986</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="22">
         <v>135418067</v>
       </c>
       <c r="E5" s="17">
         <v>3450148405</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="42" t="s">
@@ -2658,16 +2805,16 @@
       <c r="B6" s="7">
         <v>45978</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="56">
         <v>45986</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="22">
         <v>135431815</v>
       </c>
       <c r="E6" s="17">
         <v>3450149747</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G6" s="42" t="s">
@@ -2687,16 +2834,16 @@
       <c r="B7" s="7">
         <v>45980</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="56">
         <v>45986</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="22">
         <v>135475935</v>
       </c>
       <c r="E7" s="17">
         <v>3450153839</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="42" t="s">
@@ -2716,16 +2863,16 @@
       <c r="B8" s="7">
         <v>45989</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="56">
         <v>45986</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="22">
         <v>135469811</v>
       </c>
       <c r="E8" s="17">
         <v>3450153201</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="11" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="42" t="s">
@@ -2745,16 +2892,16 @@
       <c r="B9" s="7">
         <v>46004</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="56">
         <v>45986</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="22">
         <v>135475033</v>
       </c>
       <c r="E9" s="17">
         <v>3450153740</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="11" t="s">
         <v>91</v>
       </c>
       <c r="G9" s="42" t="s">
@@ -2774,22 +2921,22 @@
       <c r="B10" s="7">
         <v>45987</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="56">
         <v>45986</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="22">
         <v>135365526</v>
       </c>
       <c r="E10" s="17">
         <v>3450144247</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="11" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="66" t="s">
+      <c r="H10" s="12" t="s">
         <v>94</v>
       </c>
       <c r="I10" s="44">
@@ -2803,16 +2950,16 @@
       <c r="B11" s="7">
         <v>45980</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="56">
         <v>45986</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="22">
         <v>135466743</v>
       </c>
       <c r="E11" s="17">
         <v>3450152849</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="11" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="42" t="s">
@@ -2832,16 +2979,16 @@
       <c r="B12" s="7">
         <v>45982</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="56">
         <v>45986</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="22">
         <v>135487600</v>
       </c>
       <c r="E12" s="17">
         <v>3450154367</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G12" s="42" t="s">
@@ -2861,16 +3008,16 @@
       <c r="B13" s="7">
         <v>45995</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="56">
         <v>45986</v>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="22">
         <v>135470636</v>
       </c>
       <c r="E13" s="17">
         <v>3450153245</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="11" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="42" t="s">
@@ -2890,16 +3037,16 @@
       <c r="B14" s="7">
         <v>45982</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="56">
         <v>45986</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="22">
         <v>135491304</v>
       </c>
       <c r="E14" s="17">
         <v>3450154697</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="11" t="s">
         <v>99</v>
       </c>
       <c r="G14" s="42" t="s">
@@ -2919,16 +3066,16 @@
       <c r="B15" s="7">
         <v>45982</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="56">
         <v>45986</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="22">
         <v>135493505</v>
       </c>
       <c r="E15" s="17">
         <v>3450154994</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="11" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="42" t="s">
@@ -2948,16 +3095,16 @@
       <c r="B16" s="7">
         <v>45980</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="56">
         <v>45986</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="22">
         <v>135464753</v>
       </c>
       <c r="E16" s="17">
         <v>3450152497</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="11" t="s">
         <v>101</v>
       </c>
       <c r="G16" s="42" t="s">
@@ -2977,16 +3124,16 @@
       <c r="B17" s="7">
         <v>45982</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="56">
         <v>45986</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="22">
         <v>135490210</v>
       </c>
       <c r="E17" s="17">
         <v>3450154610</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="11" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="42" t="s">
@@ -3006,22 +3153,22 @@
       <c r="B18" s="7">
         <v>45974</v>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="56">
         <v>45986</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="22">
         <v>135423401</v>
       </c>
       <c r="E18" s="17">
         <v>3450145600</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="11" t="s">
         <v>103</v>
       </c>
       <c r="G18" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="12" t="s">
         <v>104</v>
       </c>
       <c r="I18" s="44">
@@ -3035,16 +3182,16 @@
       <c r="B19" s="7">
         <v>45985</v>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="56">
         <v>45986</v>
       </c>
-      <c r="D19" s="63">
+      <c r="D19" s="22">
         <v>135513778</v>
       </c>
       <c r="E19" s="17">
         <v>3450156810</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="11" t="s">
         <v>105</v>
       </c>
       <c r="G19" s="42" t="s">
@@ -3064,16 +3211,16 @@
       <c r="B20" s="7">
         <v>45973</v>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="56">
         <v>45986</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="22">
         <v>135371138</v>
       </c>
       <c r="E20" s="17">
         <v>3450144808</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="11" t="s">
         <v>106</v>
       </c>
       <c r="G20" s="42" t="s">
@@ -3093,16 +3240,16 @@
       <c r="B21" s="7">
         <v>45978</v>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="56">
         <v>45986</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D21" s="22">
         <v>135422961</v>
       </c>
       <c r="E21" s="17">
         <v>3450148780</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="11" t="s">
         <v>109</v>
       </c>
       <c r="G21" s="42" t="s">
@@ -3122,16 +3269,16 @@
       <c r="B22" s="7">
         <v>45979</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="56">
         <v>45986</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D22" s="22">
         <v>135465259</v>
       </c>
       <c r="E22" s="17">
         <v>3450150825</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="11" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="42" t="s">
@@ -3151,22 +3298,22 @@
       <c r="B23" s="7">
         <v>45974</v>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="56">
         <v>45986</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="22">
         <v>135384088</v>
       </c>
       <c r="E23" s="17">
         <v>3450145776</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="11" t="s">
         <v>112</v>
       </c>
       <c r="G23" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="12" t="s">
         <v>90</v>
       </c>
       <c r="I23" s="44">
@@ -3180,22 +3327,22 @@
       <c r="B24" s="7">
         <v>45974</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="56">
         <v>45986</v>
       </c>
-      <c r="D24" s="63">
+      <c r="D24" s="22">
         <v>135380282</v>
       </c>
       <c r="E24" s="17">
         <v>3450145380</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="11" t="s">
         <v>113</v>
       </c>
       <c r="G24" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="66" t="s">
+      <c r="H24" s="12" t="s">
         <v>115</v>
       </c>
       <c r="I24" s="44">
@@ -3209,16 +3356,16 @@
       <c r="B25" s="7">
         <v>45978</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="56">
         <v>45986</v>
       </c>
-      <c r="D25" s="63">
+      <c r="D25" s="22">
         <v>135424489</v>
       </c>
       <c r="E25" s="17">
         <v>3450148933</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="11" t="s">
         <v>116</v>
       </c>
       <c r="G25" s="42" t="s">
@@ -3238,16 +3385,16 @@
       <c r="B26" s="7">
         <v>45991</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="56">
         <v>45986</v>
       </c>
-      <c r="D26" s="63">
+      <c r="D26" s="22">
         <v>135421815</v>
       </c>
       <c r="E26" s="17">
         <v>3450148724</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="11" t="s">
         <v>118</v>
       </c>
       <c r="G26" s="42" t="s">
@@ -3267,16 +3414,16 @@
       <c r="B27" s="7">
         <v>45978</v>
       </c>
-      <c r="C27" s="57">
+      <c r="C27" s="56">
         <v>45986</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="22">
         <v>135427573</v>
       </c>
       <c r="E27" s="17">
         <v>3450149230</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="11" t="s">
         <v>120</v>
       </c>
       <c r="G27" s="42" t="s">
@@ -3296,16 +3443,16 @@
       <c r="B28" s="7">
         <v>45975</v>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="56">
         <v>45986</v>
       </c>
-      <c r="D28" s="63">
+      <c r="D28" s="22">
         <v>135443033</v>
       </c>
       <c r="E28" s="17">
         <v>3450147481</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="11" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="42" t="s">
@@ -3325,16 +3472,16 @@
       <c r="B29" s="7">
         <v>45982</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="56">
         <v>45986</v>
       </c>
-      <c r="D29" s="63">
+      <c r="D29" s="22">
         <v>135497978</v>
       </c>
       <c r="E29" s="17">
         <v>3450155478</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="11" t="s">
         <v>122</v>
       </c>
       <c r="G29" s="42" t="s">
@@ -3354,16 +3501,16 @@
       <c r="B30" s="7">
         <v>45979</v>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="56">
         <v>45986</v>
       </c>
-      <c r="D30" s="63">
+      <c r="D30" s="22">
         <v>135440916</v>
       </c>
       <c r="E30" s="17">
         <v>3450150210</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="11" t="s">
         <v>123</v>
       </c>
       <c r="G30" s="42" t="s">
@@ -3383,16 +3530,16 @@
       <c r="B31" s="7">
         <v>45979</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C31" s="56">
         <v>45986</v>
       </c>
-      <c r="D31" s="63">
+      <c r="D31" s="22">
         <v>135442838</v>
       </c>
       <c r="E31" s="17">
         <v>3450150484</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="11" t="s">
         <v>124</v>
       </c>
       <c r="G31" s="42" t="s">
@@ -3412,16 +3559,16 @@
       <c r="B32" s="7">
         <v>45980</v>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="56">
         <v>45986</v>
       </c>
-      <c r="D32" s="63">
+      <c r="D32" s="22">
         <v>135460460</v>
       </c>
       <c r="E32" s="17">
         <v>3450152080</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="11" t="s">
         <v>125</v>
       </c>
       <c r="G32" s="42" t="s">
@@ -3441,7 +3588,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="20"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="51"/>
+      <c r="G33" s="50"/>
       <c r="H33" s="14"/>
       <c r="I33" s="24"/>
     </row>
@@ -3468,14 +3615,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
     <col min="9" max="9" width="21" style="24" customWidth="1"/>
@@ -3514,7 +3661,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="64">
+      <c r="B2" s="61">
         <v>45991</v>
       </c>
       <c r="C2" s="25">
@@ -3532,19 +3679,20 @@
       <c r="G2" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="62" t="s">
         <v>129</v>
       </c>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="64">
+      <c r="B3" s="61">
         <v>45991</v>
       </c>
       <c r="C3" s="25">
-        <v>45982</v>
+        <v>45987</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>127</v>
@@ -3558,247 +3706,581 @@
       <c r="G3" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="46" t="s">
         <v>131</v>
       </c>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="11"/>
+      <c r="B4" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450156798</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="14"/>
+      <c r="B5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="66">
+        <v>3450156908</v>
+      </c>
+      <c r="F5" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="49" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="61">
+        <v>45975</v>
+      </c>
+      <c r="C6" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D6" s="72">
+        <v>135401884</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450147118</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="61">
+        <v>46003</v>
+      </c>
+      <c r="C7" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D7" s="72">
+        <v>135411282</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450148053</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="61">
+        <v>45978</v>
+      </c>
+      <c r="C8" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D8" s="72">
+        <v>135431683</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450149736</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="11"/>
+      <c r="B9" s="61">
+        <v>45980</v>
+      </c>
+      <c r="C9" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D9" s="72">
+        <v>135480068</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450154059</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="44">
+        <v>45980</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="61">
+        <v>45975</v>
+      </c>
+      <c r="C10" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D10" s="72">
+        <v>135413293</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450148295</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="61">
+        <v>45979</v>
+      </c>
+      <c r="C11" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D11" s="72">
+        <v>135489165</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450151353</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="44">
+        <v>45979</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="61">
+        <v>45989</v>
+      </c>
+      <c r="C12" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D12" s="72">
+        <v>135537702</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450155940</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="61">
+        <v>45974</v>
+      </c>
+      <c r="C13" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D13" s="72">
+        <v>135377794</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450145182</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="61">
+        <v>45973</v>
+      </c>
+      <c r="C14" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D14" s="72">
+        <v>135360568</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450143862</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="44">
+        <v>45986</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="61">
+        <v>45974</v>
+      </c>
+      <c r="C15" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D15" s="72">
+        <v>135380046</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450145369</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="44">
+        <v>45985</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="B16" s="61">
+        <v>45980</v>
+      </c>
+      <c r="C16" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D16" s="72">
+        <v>135465358</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450152618</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="44">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="61">
+        <v>45982</v>
+      </c>
+      <c r="C17" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D17" s="72">
+        <v>135486931</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450154301</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="44">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C18" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D18" s="72">
+        <v>135472368</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450153421</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I18" s="44">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C19" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D19" s="72">
+        <v>135447654</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450150957</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="44">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C20" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D20" s="72">
+        <v>135466143</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450152772</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I20" s="44">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C21" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D21" s="72">
+        <v>135444405</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450150660</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="44">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45977</v>
+      </c>
+      <c r="C22" s="25">
+        <v>45987</v>
+      </c>
+      <c r="D22" s="72">
+        <v>135416666</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450148361</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="44">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="D23" s="70"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="22"/>
+      <c r="D24" s="26"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="21"/>
+      <c r="G24" s="19"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="25"/>
@@ -3808,37 +4290,37 @@
       <c r="G25" s="19"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="19"/>
+      <c r="G26" s="21"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="26"/>
+      <c r="D27" s="22"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="19"/>
+      <c r="G27" s="21"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
+      <c r="D28" s="22"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="19"/>
+      <c r="G28" s="21"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="25"/>
@@ -3848,7 +4330,7 @@
       <c r="G29" s="21"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="25"/>
@@ -3858,7 +4340,7 @@
       <c r="G30" s="21"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="25"/>
@@ -3868,7 +4350,7 @@
       <c r="G31" s="21"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="25"/>
@@ -3890,41 +4372,41 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="21"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="21"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="21"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="14"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
@@ -3958,53 +4440,23 @@
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B20" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6471,67 +6923,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="cda820598d61c00a5299587a11c0dc14">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0803c1971eb453546b9f8a0aa56ab91b" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6580,12 +6973,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6594,12 +6987,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6682,7 +7075,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6701,7 +7094,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6734,7 +7127,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6817,8 +7210,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6907,6 +7300,65 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6951,7 +7403,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6959,7 +7411,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2EF5E87-F613-441E-A63A-5260576F6967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
